--- a/output/pdf_financials_xlsx/AIVC.xlsx
+++ b/output/pdf_financials_xlsx/AIVC.xlsx
@@ -4866,37 +4866,37 @@
         <v>0.647632</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.647632</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.647632</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.692867</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.492522</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.492522</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.729772</v>
       </c>
     </row>
     <row r="93">
@@ -7874,7 +7874,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.59221</v>
       </c>

--- a/output/pdf_financials_xlsx/AIVC.xlsx
+++ b/output/pdf_financials_xlsx/AIVC.xlsx
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.01724</v>
+        <v>0.444679</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.017093</v>
+        <v>0.125901</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.116338</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.09394</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.968438</v>
+        <v>3.032577</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.75482</v>
+        <v>0.884935</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.206926</v>
+        <v>0.575122</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.742981</v>
+        <v>0.890697</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.219499</v>
+        <v>0.301927</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.136301</v>
+        <v>0.261525</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.077627</v>
+        <v>0.117737</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.102104</v>
+        <v>0.168694</v>
       </c>
     </row>
     <row r="11">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.006279</v>
+        <v>-0.115087</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.819499</v>
+        <v>1.451303</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5.254339</v>
+        <v>5.106623</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -2121,34 +2121,34 @@
         <v>0.001183</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.08207200000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.14617</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.171471</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.037369</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.932982</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.055657</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.187988</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.08400299999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.114022</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.133983</v>
       </c>
     </row>
     <row r="35">
@@ -2213,34 +2213,34 @@
         <v>0.001183</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.08207200000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.14617</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.171471</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.037369</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.932982</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.055657</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.187988</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.08400299999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.114022</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.133983</v>
       </c>
     </row>
     <row r="37">
@@ -2765,10 +2765,10 @@
         <v>0.005422</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.132072</v>
+        <v>0.05</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.43317</v>
+        <v>0.287</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2777,22 +2777,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.921041</v>
+        <v>3.988059</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>10.55204</v>
+        <v>10.496383</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.100507</v>
+        <v>4.912519</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.29083</v>
+        <v>3.206827</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.427877</v>
+        <v>2.313855</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.901601</v>
+        <v>3.767618</v>
       </c>
     </row>
     <row r="49">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">

--- a/output/pdf_financials_xlsx/AIVC.xlsx
+++ b/output/pdf_financials_xlsx/AIVC.xlsx
@@ -606,10 +606,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -720,10 +718,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.018738</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.01724</v>
@@ -768,10 +764,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -816,10 +810,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -864,10 +856,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.523801</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.444679</v>
@@ -978,10 +968,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1026,10 +1014,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -1074,10 +1060,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1122,10 +1106,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-1.087282</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>-0.812391</v>
@@ -1170,10 +1152,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.82003</v>
@@ -1218,10 +1198,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1410,10 +1388,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.82003</v>
@@ -1458,10 +1434,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1506,10 +1480,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1554,10 +1526,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.82003</v>
@@ -1602,10 +1572,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.52</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.1</v>
@@ -1664,10 +1632,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.52</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.1</v>
@@ -1726,10 +1692,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>2.117346</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>8.2003</v>
@@ -1780,10 +1744,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.82003</v>
@@ -1828,10 +1790,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1876,10 +1836,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.82003</v>
@@ -1990,10 +1948,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3535,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.142105</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.187352</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -3673,10 +3629,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -5142,10 +5098,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.82003</v>
@@ -5190,10 +5144,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5238,10 +5190,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -5286,10 +5236,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -5334,10 +5282,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.01013</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.001918</v>
@@ -5382,10 +5328,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.064441</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.186796</v>
@@ -5430,10 +5374,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5478,10 +5420,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.074571</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.184878</v>
@@ -5526,10 +5466,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -5574,10 +5512,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5622,10 +5558,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5670,10 +5604,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5718,10 +5650,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5766,10 +5696,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5814,10 +5742,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5862,46 +5788,44 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.06005</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.192983</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.242665</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.312507</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-8.933052999999999</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-1.909838</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-1.604195</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-6.570135</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.916493</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.604729</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.81953</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.484405</v>
       </c>
     </row>
     <row r="115">
@@ -5910,46 +5834,44 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0.834126</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.049588</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.060322</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.113495</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.764063</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.868537</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.45527</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>6.04307</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.750753</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.7902130000000001</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.859834</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.805688</v>
       </c>
     </row>
     <row r="116">
@@ -5958,10 +5880,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -6006,10 +5926,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -6054,10 +5972,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -6102,10 +6018,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.06005</v>
@@ -6150,10 +6064,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -6198,10 +6110,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -6246,10 +6156,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -6294,10 +6202,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -6342,10 +6248,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -6390,10 +6294,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -6438,10 +6340,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -6558,10 +6458,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.023216</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>-0.05685</v>
@@ -6606,10 +6504,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.381113</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.5434</v>
@@ -6654,10 +6550,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.121823</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.053706</v>
@@ -6702,10 +6596,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -6750,10 +6642,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.068117</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.211384</v>
@@ -6798,10 +6688,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.053706</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.26509</v>
@@ -6846,10 +6734,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6894,10 +6780,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.44923</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.271966</v>
@@ -6947,7 +6831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q227"/>
+  <dimension ref="A1:Q234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11224,10 +11108,8 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>0.590957</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>0.300172</v>
@@ -11830,10 +11712,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.064441</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0.186796</v>
@@ -11968,10 +11848,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>-0.44923</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>-0.271966</v>
@@ -12026,7 +11904,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -12243,7 +12125,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -12882,10 +12768,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="5" t="n">
+        <v>0.01013</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>-0.001918</v>
@@ -13032,10 +12916,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="5" t="n">
+        <v>0.381113</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0.5434</v>
@@ -14889,7 +14771,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -14968,7 +14854,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -15293,15 +15183,11 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="5" t="n">
+        <v>-1.10102</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-0.846332</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -16897,10 +16783,8 @@
           <t>NetOtherFinancingCharges</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="5" t="n">
+        <v>-0.023216</v>
       </c>
       <c r="F129" s="5" t="n">
         <v>-0.05685</v>
@@ -17303,7 +17187,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -17389,10 +17277,8 @@
           <t>CommonStockIssuance</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="5" t="n">
+        <v>0.404329</v>
       </c>
       <c r="F135" s="5" t="n">
         <v>0.60025</v>
@@ -17474,10 +17360,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" s="5" t="n">
+        <v>-0.068117</v>
       </c>
       <c r="F136" s="5" t="n">
         <v>0.211384</v>
@@ -17557,10 +17441,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E137" s="5" t="n">
+        <v>0.121823</v>
       </c>
       <c r="F137" s="5" t="n">
         <v>0.053706</v>
@@ -17640,10 +17522,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E138" s="5" t="n">
+        <v>0.053706</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>0.26509</v>
@@ -17719,10 +17599,8 @@
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E139" s="5" t="n">
+        <v>0.003706</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>0.001397</v>
@@ -17879,10 +17757,8 @@
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E141" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="F141" s="5" t="n">
         <v>0.263693</v>
@@ -17960,10 +17836,8 @@
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E142" s="5" t="n">
+        <v>0.053706</v>
       </c>
       <c r="F142" s="5" t="n">
         <v>0.26509</v>
@@ -18201,10 +18075,8 @@
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E145" s="5" t="n">
+        <v>0.006166</v>
       </c>
       <c r="F145" s="5" t="n">
         <v>0.055422</v>
@@ -18281,7 +18153,11 @@
           <t>Issuance of note payable for acquisition of investments</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -18349,25 +18225,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Items not involving cash</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of investments</t>
+          <t>Unrealized foreign exchange gain</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E147" s="5" t="n">
+        <v>-0.013738</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>-0.007639</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -18409,33 +18285,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O147" s="5" t="n">
-        <v>-0.148102</v>
-      </c>
-      <c r="P147" s="5" t="n">
-        <v>0.06578199999999999</v>
-      </c>
-      <c r="Q147" s="5" t="n">
-        <v>0.170962</v>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Non-cash investing and financing activities</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Interest revenue</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Fair value of shares received for sale of investment</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.834126</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18447,35 +18335,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="5" t="n">
-        <v>0.006929</v>
-      </c>
-      <c r="I148" s="5" t="n">
-        <v>0.056599</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>0.069288</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0.025793</v>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v>0.0322</v>
-      </c>
-      <c r="M148" s="5" t="n">
-        <v>0.02774</v>
-      </c>
-      <c r="N148" s="5" t="n">
-        <v>0.016865</v>
-      </c>
-      <c r="O148" s="5" t="n">
-        <v>0.026974</v>
-      </c>
-      <c r="P148" s="5" t="n">
-        <v>0.017737</v>
-      </c>
-      <c r="Q148" s="5" t="n">
-        <v>0.031438</v>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -18487,14 +18395,10 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on investments</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
+          <t>Gain (loss) on sale of investments</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18530,23 +18434,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L149" s="5" t="n">
-        <v>3.266409</v>
-      </c>
-      <c r="M149" s="5" t="n">
-        <v>2.961091</v>
-      </c>
-      <c r="N149" s="5" t="n">
-        <v>-5.43293</v>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O149" s="5" t="n">
-        <v>-1.478879</v>
+        <v>-0.148102</v>
       </c>
       <c r="P149" s="5" t="n">
-        <v>-0.999677</v>
+        <v>0.06578199999999999</v>
       </c>
       <c r="Q149" s="5" t="n">
-        <v>1.505856</v>
+        <v>0.170962</v>
       </c>
     </row>
     <row r="150">
@@ -18555,19 +18465,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 7)</t>
+          <t>Interest revenue</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncome</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -18585,51 +18491,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>0.006929</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>0.056599</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>0.069288</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>0.025793</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="M150" s="5" t="n">
+        <v>0.02774</v>
+      </c>
+      <c r="N150" s="5" t="n">
+        <v>0.016865</v>
+      </c>
+      <c r="O150" s="5" t="n">
+        <v>0.026974</v>
       </c>
       <c r="P150" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.017737</v>
       </c>
       <c r="Q150" s="5" t="n">
-        <v>0.078</v>
+        <v>0.031438</v>
       </c>
     </row>
     <row r="151">
@@ -18638,19 +18528,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Unrealized gain (loss) on investments</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetRealizedGainLossOnInvestments</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -18658,11 +18544,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F151" s="5" t="n">
-        <v>0.01724</v>
-      </c>
-      <c r="G151" s="5" t="n">
-        <v>0.017093</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -18685,22 +18575,22 @@
         </is>
       </c>
       <c r="L151" s="5" t="n">
-        <v>0.074349</v>
+        <v>3.266409</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>0.037418</v>
+        <v>2.961091</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>0.037768</v>
+        <v>-5.43293</v>
       </c>
       <c r="O151" s="5" t="n">
-        <v>0.014634</v>
+        <v>-1.478879</v>
       </c>
       <c r="P151" s="5" t="n">
-        <v>0.026127</v>
+        <v>-0.999677</v>
       </c>
       <c r="Q151" s="5" t="n">
-        <v>0.024104</v>
+        <v>1.505856</v>
       </c>
     </row>
     <row r="152">
@@ -18716,12 +18606,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Consulting fees (Note 7)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -18739,35 +18629,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H152" s="5" t="n">
-        <v>0.082827</v>
-      </c>
-      <c r="I152" s="5" t="n">
-        <v>0.008498</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>0.010434</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>0.051179</v>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v>0.019364</v>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v>0.031837</v>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v>0.001046</v>
-      </c>
-      <c r="O152" s="5" t="n">
-        <v>0.009734</v>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P152" s="5" t="n">
-        <v>0.001103</v>
+        <v>0.0515</v>
       </c>
       <c r="Q152" s="5" t="n">
-        <v>0.000915</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="153">
@@ -18783,28 +18689,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>0.018738</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.01724</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.017093</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -18826,31 +18726,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L153" s="5" t="n">
+        <v>0.074349</v>
+      </c>
+      <c r="M153" s="5" t="n">
+        <v>0.037418</v>
+      </c>
+      <c r="N153" s="5" t="n">
+        <v>0.037768</v>
+      </c>
+      <c r="O153" s="5" t="n">
+        <v>0.014634</v>
       </c>
       <c r="P153" s="5" t="n">
-        <v>0.039007</v>
+        <v>0.026127</v>
       </c>
       <c r="Q153" s="5" t="n">
-        <v>0.065675</v>
+        <v>0.024104</v>
       </c>
     </row>
     <row r="154">
@@ -18866,12 +18758,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -18879,41 +18771,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F154" s="5" t="n">
-        <v>0.444679</v>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>0.125901</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.116338</v>
+        <v>0.082827</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>0.09394</v>
+        <v>0.008498</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>3.032577</v>
+        <v>0.010434</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>0.884935</v>
+        <v>0.051179</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>0.575122</v>
+        <v>0.019364</v>
       </c>
       <c r="M154" s="5" t="n">
-        <v>0.890697</v>
+        <v>0.031837</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>0.301927</v>
+        <v>0.001046</v>
       </c>
       <c r="O154" s="5" t="n">
-        <v>0.261525</v>
+        <v>0.009734</v>
       </c>
       <c r="P154" s="5" t="n">
-        <v>0.117737</v>
+        <v>0.001103</v>
       </c>
       <c r="Q154" s="5" t="n">
-        <v>0.168694</v>
+        <v>0.000915</v>
       </c>
     </row>
     <row r="155">
@@ -18929,12 +18825,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Income (loss) before other income (expense)</t>
+          <t>Professional fees (Note 7)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -18982,17 +18878,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N155" s="5" t="n">
-        <v>-5.440428</v>
-      </c>
-      <c r="O155" s="5" t="n">
-        <v>-1.861532</v>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P155" s="5" t="n">
-        <v>-1.033895</v>
+        <v>0.039007</v>
       </c>
       <c r="Q155" s="5" t="n">
-        <v>1.539562</v>
+        <v>0.065675</v>
       </c>
     </row>
     <row r="156">
@@ -19003,77 +18903,57 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Impairment of loan receivable</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.523801</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.444679</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.125901</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.116338</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.09394</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>3.032577</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>0.884935</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>0.575122</v>
+      </c>
+      <c r="M156" s="5" t="n">
+        <v>0.890697</v>
+      </c>
+      <c r="N156" s="5" t="n">
+        <v>0.301927</v>
+      </c>
+      <c r="O156" s="5" t="n">
+        <v>0.261525</v>
       </c>
       <c r="P156" s="5" t="n">
-        <v>-0.1254</v>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.117737</v>
+      </c>
+      <c r="Q156" s="5" t="n">
+        <v>0.168694</v>
       </c>
     </row>
     <row r="157">
@@ -19084,15 +18964,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 4)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Income (loss) before other income (expense)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -19138,23 +19022,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N157" s="5" t="n">
+        <v>-5.440428</v>
+      </c>
+      <c r="O157" s="5" t="n">
+        <v>-1.861532</v>
+      </c>
+      <c r="P157" s="5" t="n">
+        <v>-1.033895</v>
       </c>
       <c r="Q157" s="5" t="n">
-        <v>1e-06</v>
+        <v>1.539562</v>
       </c>
     </row>
     <row r="158">
@@ -19170,7 +19048,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Business development</t>
+          <t>Impairment of loan receivable</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -19230,7 +19108,7 @@
         </is>
       </c>
       <c r="P158" s="5" t="n">
-        <v>-0.227505</v>
+        <v>-0.1254</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -19251,7 +19129,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Gain on write-off of accounts payable</t>
+          <t>Impairment of mineral properties (Note 4)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -19316,7 +19194,7 @@
         </is>
       </c>
       <c r="Q159" s="5" t="n">
-        <v>0.210036</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="160">
@@ -19332,7 +19210,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 6a)</t>
+          <t>Business development</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -19392,7 +19270,7 @@
         </is>
       </c>
       <c r="P160" s="5" t="n">
-        <v>0.185</v>
+        <v>-0.227505</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -19413,54 +19291,72 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Gain on write-off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F161" s="5" t="n">
-        <v>-0.012165</v>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>-0.01473</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>-0.013284</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>-0.023245</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>-0.016914</v>
-      </c>
-      <c r="K161" s="5" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v>-0.015181</v>
-      </c>
-      <c r="M161" s="5" t="n">
-        <v>-0.01751</v>
-      </c>
-      <c r="N161" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v>-0.0007159999999999999</v>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v>-0.003938</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q161" s="5" t="n">
-        <v>-0.014255</v>
+        <v>0.210036</v>
       </c>
     </row>
     <row r="162">
@@ -19476,54 +19372,72 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Total other income (expense)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement (Note 6a)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F162" s="5" t="n">
-        <v>-0.375351</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>0.213298</v>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>0.110357</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>0.300193</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>-7.14611</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>-2.95254</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>0.345732</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>-6.405509</v>
-      </c>
-      <c r="N162" s="5" t="n">
-        <v>-0.064554</v>
-      </c>
-      <c r="O162" s="5" t="n">
-        <v>-0.200716</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P162" s="5" t="n">
-        <v>-0.171843</v>
-      </c>
-      <c r="Q162" s="5" t="n">
-        <v>0.195782</v>
+        <v>0.185</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -19539,12 +19453,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss)</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -19552,57 +19466,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F163" s="5" t="n">
+        <v>-0.012165</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>-0.01473</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>-0.013284</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>-0.023245</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>-0.016914</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>-0.015181</v>
+      </c>
+      <c r="M163" s="5" t="n">
+        <v>-0.01751</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>-5.504982</v>
+        <v>-0.0075</v>
       </c>
       <c r="O163" s="5" t="n">
-        <v>-2.062248</v>
+        <v>-0.0007159999999999999</v>
       </c>
       <c r="P163" s="5" t="n">
-        <v>-1.205738</v>
+        <v>-0.003938</v>
       </c>
       <c r="Q163" s="5" t="n">
-        <v>1.735344</v>
+        <v>-0.014255</v>
       </c>
     </row>
     <row r="164">
@@ -19613,75 +19511,57 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Basic (Note 8d)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total other income (expense)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>-0.577219</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>-0.375351</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.213298</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.110357</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.300193</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>-7.14611</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>-2.95254</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>0.345732</v>
+      </c>
+      <c r="M164" s="5" t="n">
+        <v>-6.405509</v>
+      </c>
+      <c r="N164" s="5" t="n">
+        <v>-0.064554</v>
+      </c>
+      <c r="O164" s="5" t="n">
+        <v>-0.200716</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.171843</v>
       </c>
       <c r="Q164" s="5" t="n">
-        <v>5e-08</v>
+        <v>0.195782</v>
       </c>
     </row>
     <row r="165">
@@ -19692,15 +19572,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Diluted (Note 8d)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -19746,21 +19630,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N165" s="5" t="n">
+        <v>-5.504982</v>
+      </c>
+      <c r="O165" s="5" t="n">
+        <v>-2.062248</v>
       </c>
       <c r="P165" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-1.205738</v>
       </c>
       <c r="Q165" s="5" t="n">
-        <v>5e-08</v>
+        <v>1.735344</v>
       </c>
     </row>
     <row r="166">
@@ -19771,7 +19651,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -19779,11 +19659,7 @@
           <t>Basic (Note 8d)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -19840,10 +19716,10 @@
         </is>
       </c>
       <c r="P166" s="5" t="n">
-        <v>32.025453</v>
+        <v>-4e-08</v>
       </c>
       <c r="Q166" s="5" t="n">
-        <v>32.025453</v>
+        <v>5e-08</v>
       </c>
     </row>
     <row r="167">
@@ -19854,7 +19730,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -19862,11 +19738,7 @@
           <t>Diluted (Note 8d)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -19923,10 +19795,10 @@
         </is>
       </c>
       <c r="P167" s="5" t="n">
-        <v>32.025453</v>
+        <v>-4e-08</v>
       </c>
       <c r="Q167" s="5" t="n">
-        <v>32.025453</v>
+        <v>5e-08</v>
       </c>
     </row>
     <row r="168">
@@ -19937,17 +19809,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 8)</t>
+          <t>Basic (Note 8d)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -19985,25 +19857,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L168" s="5" t="n">
-        <v>0.132577</v>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v>0.7055630000000001</v>
-      </c>
-      <c r="N168" s="5" t="n">
-        <v>0.181731</v>
-      </c>
-      <c r="O168" s="5" t="n">
-        <v>0.121667</v>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P168" s="5" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.025453</v>
+      </c>
+      <c r="Q168" s="5" t="n">
+        <v>32.025453</v>
       </c>
     </row>
     <row r="169">
@@ -20014,17 +19892,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Professional fees (Note 8)</t>
+          <t>Diluted (Note 8d)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -20042,11 +19920,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="5" t="n">
-        <v>0.033511</v>
-      </c>
-      <c r="I169" s="5" t="n">
-        <v>0.040207</v>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -20058,25 +19940,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L169" s="5" t="n">
-        <v>0.141601</v>
-      </c>
-      <c r="M169" s="5" t="n">
-        <v>0.115879</v>
-      </c>
-      <c r="N169" s="5" t="n">
-        <v>0.081382</v>
-      </c>
-      <c r="O169" s="5" t="n">
-        <v>0.11549</v>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P169" s="5" t="n">
-        <v>0.039007</v>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.025453</v>
+      </c>
+      <c r="Q169" s="5" t="n">
+        <v>32.025453</v>
       </c>
     </row>
     <row r="170">
@@ -20087,15 +19975,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Impairment of loan receivable (Note 5)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Consulting fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -20131,26 +20023,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L170" s="5" t="n">
+        <v>0.132577</v>
+      </c>
+      <c r="M170" s="5" t="n">
+        <v>0.7055630000000001</v>
+      </c>
+      <c r="N170" s="5" t="n">
+        <v>0.181731</v>
       </c>
       <c r="O170" s="5" t="n">
-        <v>-0.2</v>
+        <v>0.121667</v>
       </c>
       <c r="P170" s="5" t="n">
-        <v>-0.1254</v>
+        <v>0.0515</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -20166,15 +20052,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 7a)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Professional fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -20190,15 +20080,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H171" s="5" t="n">
+        <v>0.033511</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.040207</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -20210,28 +20096,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L171" s="5" t="n">
+        <v>0.141601</v>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>0.115879</v>
+      </c>
+      <c r="N171" s="5" t="n">
+        <v>0.081382</v>
+      </c>
+      <c r="O171" s="5" t="n">
+        <v>0.11549</v>
       </c>
       <c r="P171" s="5" t="n">
-        <v>0.185</v>
+        <v>0.039007</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -20252,24 +20130,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment of loan receivable (Note 5)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F172" s="5" t="n">
-        <v>-0.82003</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>0.09821100000000001</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -20291,20 +20169,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L172" s="5" t="n">
-        <v>1.797035</v>
-      </c>
-      <c r="M172" s="5" t="n">
-        <v>-1.298886</v>
-      </c>
-      <c r="N172" s="5" t="n">
-        <v>-5.504982</v>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O172" s="5" t="n">
-        <v>-2.062248</v>
+        <v>-0.2</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>-1.205738</v>
+        <v>-0.1254</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -20325,7 +20209,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Gain on debt settlement (Note 7a)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -20374,14 +20258,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N173" s="5" t="n">
-        <v>-5.504982</v>
-      </c>
-      <c r="O173" s="5" t="n">
-        <v>-2.058272</v>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P173" s="5" t="n">
-        <v>-1.205738</v>
+        <v>0.185</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -20402,12 +20290,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Net income (loss) and comprehensive income (loss) for the year</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -20415,15 +20303,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F174" s="5" t="n">
+        <v>-0.82003</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.09821100000000001</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -20445,28 +20329,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L174" s="5" t="n">
+        <v>1.797035</v>
+      </c>
+      <c r="M174" s="5" t="n">
+        <v>-1.298886</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>-5.504982</v>
       </c>
       <c r="O174" s="5" t="n">
-        <v>0.003976</v>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.062248</v>
+      </c>
+      <c r="P174" s="5" t="n">
+        <v>-1.205738</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -20482,12 +20358,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Basic (Note 9d)</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -20531,17 +20407,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M175" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N175" s="5" t="n">
-        <v>-1.8e-07</v>
+        <v>-5.504982</v>
       </c>
       <c r="O175" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-2.058272</v>
       </c>
       <c r="P175" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-1.205738</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -20557,15 +20435,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Diluted (Note 9d)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -20606,17 +20488,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M176" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="N176" s="5" t="n">
-        <v>-1.8e-07</v>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O176" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="P176" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.003976</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
@@ -20632,7 +20520,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20640,11 +20528,7 @@
           <t>Basic (Note 9d)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -20686,16 +20570,16 @@
         </is>
       </c>
       <c r="M177" s="5" t="n">
-        <v>29.490638</v>
+        <v>-4e-08</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>30.549641</v>
+        <v>-1.8e-07</v>
       </c>
       <c r="O177" s="5" t="n">
-        <v>31.89212</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="P177" s="5" t="n">
-        <v>32.025453</v>
+        <v>-4e-08</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -20711,7 +20595,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -20719,11 +20603,7 @@
           <t>Diluted (Note 9d)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20765,16 +20645,16 @@
         </is>
       </c>
       <c r="M178" s="5" t="n">
-        <v>29.490638</v>
+        <v>-4e-08</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>30.549641</v>
+        <v>-1.8e-07</v>
       </c>
       <c r="O178" s="5" t="n">
-        <v>31.89212</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="P178" s="5" t="n">
-        <v>32.025453</v>
+        <v>-4e-08</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -20788,13 +20668,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gain (Loss) on sale of investments</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Basic (Note 9d)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -20830,22 +20718,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L179" s="5" t="n">
-        <v>-1.272184</v>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M179" s="5" t="n">
-        <v>2.324762</v>
+        <v>29.490638</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.277564</v>
+        <v>30.549641</v>
       </c>
       <c r="O179" s="5" t="n">
-        <v>-0.148102</v>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.89212</v>
+      </c>
+      <c r="P179" s="5" t="n">
+        <v>32.025453</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -20861,15 +20749,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Impairment of investments (Note 5)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Diluted (Note 9d)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -20910,23 +20802,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M180" s="5" t="n">
+        <v>29.490638</v>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>30.549641</v>
       </c>
       <c r="O180" s="5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.89212</v>
+      </c>
+      <c r="P180" s="5" t="n">
+        <v>32.025453</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -20940,14 +20826,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Other income (expense)</t>
-        </is>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Write-off of taxes receivable</t>
+          <t>Gain (Loss) on sale of investments</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -20986,23 +20868,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L181" s="5" t="n">
+        <v>-1.272184</v>
+      </c>
+      <c r="M181" s="5" t="n">
+        <v>2.324762</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>-0.057054</v>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.277564</v>
+      </c>
+      <c r="O181" s="5" t="n">
+        <v>-0.148102</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -21021,10 +20897,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Gain on debt assignment (Note 7b)</t>
+          <t>Impairment of investments (Note 5)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -21068,18 +20948,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M182" s="5" t="n">
-        <v>0.539983</v>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O182" s="5" t="n">
+        <v>-0.2</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -21098,10 +20978,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 5a)</t>
+          <t>Write-off of taxes receivable</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -21145,13 +21029,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M183" s="5" t="n">
-        <v>0.143744</v>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="n">
+        <v>-0.057054</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -21175,21 +21059,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Gain (loss) before other income (expense)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on debt assignment (Note 7b)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -21231,10 +21107,12 @@
         </is>
       </c>
       <c r="M184" s="5" t="n">
-        <v>5.106623</v>
-      </c>
-      <c r="N184" s="5" t="n">
-        <v>-5.440428</v>
+        <v>0.539983</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -21258,14 +21136,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Other income (expense)</t>
-        </is>
-      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Impairment of investments (Note 4)</t>
+          <t>Gain on debt settlement (Note 5a)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -21310,7 +21184,7 @@
         </is>
       </c>
       <c r="M185" s="5" t="n">
-        <v>-6.387999</v>
+        <v>0.143744</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -21339,13 +21213,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Gain on debt assignment (Note 7c)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Gain (loss) before other income (expense)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -21387,12 +21269,10 @@
         </is>
       </c>
       <c r="M186" s="5" t="n">
-        <v>0.539983</v>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.106623</v>
+      </c>
+      <c r="N186" s="5" t="n">
+        <v>-5.440428</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -21416,17 +21296,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Total Revenue *</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Impairment of investments (Note 4)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -21462,11 +21342,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L187" s="5" t="n">
-        <v>2.026425</v>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M187" s="5" t="n">
-        <v>5.99732</v>
+        <v>-6.387999</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -21495,14 +21377,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Gain on debt assignment (Note 7c)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -21541,13 +21419,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L188" s="5" t="n">
-        <v>0.207231</v>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" s="5" t="n">
+        <v>0.539983</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -21576,19 +21454,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Gain before other income (expense)</t>
+          <t>Total Revenue *</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -21627,10 +21501,10 @@
         </is>
       </c>
       <c r="L189" s="5" t="n">
-        <v>1.451303</v>
+        <v>2.026425</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>5.106623</v>
+        <v>5.99732</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -21661,12 +21535,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Write-down of accounts payable</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -21700,11 +21574,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K190" s="5" t="n">
-        <v>0.027104</v>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L190" s="5" t="n">
-        <v>0.003413</v>
+        <v>0.207231</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -21740,15 +21616,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Recapture (write-down) of loans (Note 5c,d)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Gain before other income (expense)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -21785,12 +21665,10 @@
         </is>
       </c>
       <c r="L191" s="5" t="n">
-        <v>0.3575</v>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.451303</v>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>5.106623</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -21821,12 +21699,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Basic (Note 9e)</t>
+          <t>Write-down of accounts payable</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -21860,16 +21738,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K192" s="5" t="n">
+        <v>0.027104</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>8e-08</v>
-      </c>
-      <c r="M192" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.003413</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
@@ -21900,12 +21778,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Earning (Loss) per share</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Diluted (Note 9e)</t>
+          <t>Recapture (write-down) of loans (Note 5c,d)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -21945,10 +21823,12 @@
         </is>
       </c>
       <c r="L193" s="5" t="n">
-        <v>7e-08</v>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.3575</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -21979,7 +21859,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -21987,11 +21867,7 @@
           <t>Basic (Note 9e)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -22028,10 +21904,10 @@
         </is>
       </c>
       <c r="L194" s="5" t="n">
-        <v>23.881391</v>
+        <v>8e-08</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>29.490638</v>
+        <v>-4e-08</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -22062,7 +21938,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earning (Loss) per share</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -22070,11 +21946,7 @@
           <t>Diluted (Note 9e)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -22111,10 +21983,10 @@
         </is>
       </c>
       <c r="L195" s="5" t="n">
-        <v>25.455956</v>
+        <v>7e-08</v>
       </c>
       <c r="M195" s="5" t="n">
-        <v>29.490638</v>
+        <v>-4e-08</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -22145,17 +22017,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 6)</t>
+          <t>Basic (Note 9e)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22183,21 +22055,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J196" s="5" t="n">
-        <v>0.812051</v>
-      </c>
-      <c r="K196" s="5" t="n">
-        <v>0.530595</v>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>23.881391</v>
+      </c>
+      <c r="M196" s="5" t="n">
+        <v>29.490638</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -22228,17 +22100,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Diluted (Note 9e)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -22266,21 +22138,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J197" s="5" t="n">
-        <v>0.910413</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>0.038651</v>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>25.455956</v>
+      </c>
+      <c r="M197" s="5" t="n">
+        <v>29.490638</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
@@ -22316,12 +22188,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Professional fees (Note 6)</t>
+          <t>Consulting fees (Note 6)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -22350,10 +22222,10 @@
         </is>
       </c>
       <c r="J198" s="5" t="n">
-        <v>0.208815</v>
+        <v>0.812051</v>
       </c>
       <c r="K198" s="5" t="n">
-        <v>0.07893600000000001</v>
+        <v>0.530595</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -22399,10 +22271,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 6 and 9)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -22429,12 +22305,10 @@
         </is>
       </c>
       <c r="J199" s="5" t="n">
-        <v>0.84489</v>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.910413</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>0.038651</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -22480,12 +22354,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Travel (Note 6)</t>
+          <t>Professional fees (Note 6)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -22514,10 +22388,10 @@
         </is>
       </c>
       <c r="J200" s="5" t="n">
-        <v>0.245974</v>
+        <v>0.208815</v>
       </c>
       <c r="K200" s="5" t="n">
-        <v>0.185574</v>
+        <v>0.07893600000000001</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -22563,36 +22437,42 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Loss before other income (expense)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (Notes 6 and 9)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F201" s="5" t="n">
-        <v>-0.444679</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>-0.115087</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>-0.109409</v>
-      </c>
-      <c r="I201" s="5" t="n">
-        <v>-0.037341</v>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J201" s="5" t="n">
-        <v>-2.963289</v>
-      </c>
-      <c r="K201" s="5" t="n">
-        <v>-0.859142</v>
+        <v>0.84489</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -22633,37 +22513,49 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Adjustments to fair value of investments (Note 3)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Travel (Note 6)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F202" s="5" t="n">
-        <v>-0.300172</v>
-      </c>
-      <c r="G202" s="5" t="n">
-        <v>0.209288</v>
-      </c>
-      <c r="H202" s="5" t="n">
-        <v>0.207354</v>
-      </c>
-      <c r="I202" s="5" t="n">
-        <v>0.445314</v>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J202" s="5" t="n">
-        <v>-2.457494</v>
+        <v>0.245974</v>
       </c>
       <c r="K202" s="5" t="n">
-        <v>-0.348432</v>
+        <v>0.185574</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -22704,45 +22596,39 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Impairment of investments (Note 3)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before other income (expense)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>-0.523801</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-0.444679</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>-0.115087</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>-0.109409</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>-0.037341</v>
       </c>
       <c r="J203" s="5" t="n">
-        <v>-3.509009</v>
+        <v>-2.963289</v>
       </c>
       <c r="K203" s="5" t="n">
-        <v>-0.81396</v>
+        <v>-0.859142</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -22788,36 +22674,30 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Loss on sale of investments (Note 3)</t>
+          <t>Adjustments to fair value of investments (Note 3)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E204" s="5" t="n">
+        <v>-0.590957</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>-0.300172</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.209288</v>
       </c>
       <c r="H204" s="5" t="n">
-        <v>-0.073409</v>
+        <v>0.207354</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>-0.117076</v>
+        <v>0.445314</v>
       </c>
       <c r="J204" s="5" t="n">
-        <v>-0.799693</v>
+        <v>-2.457494</v>
       </c>
       <c r="K204" s="5" t="n">
-        <v>-1.141858</v>
+        <v>-0.348432</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -22863,7 +22743,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Write-down of loans and interest receivable (Note 4)</t>
+          <t>Impairment of investments (Note 3)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -22893,10 +22773,10 @@
         </is>
       </c>
       <c r="J205" s="5" t="n">
-        <v>-0.363</v>
+        <v>-3.509009</v>
       </c>
       <c r="K205" s="5" t="n">
-        <v>-0.660394</v>
+        <v>-0.81396</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -22942,14 +22822,10 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on sale of investments (Note 3)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -22965,21 +22841,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H206" s="5" t="n">
+        <v>-0.073409</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>-0.117076</v>
       </c>
       <c r="J206" s="5" t="n">
-        <v>-10.109399</v>
+        <v>-0.799693</v>
       </c>
       <c r="K206" s="5" t="n">
-        <v>-3.811682</v>
+        <v>-1.141858</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -23025,14 +22897,10 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down of loans and interest receivable (Note 4)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -23059,10 +22927,10 @@
         </is>
       </c>
       <c r="J207" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>-0.363</v>
       </c>
       <c r="K207" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.660394</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -23108,36 +22976,40 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>-1.10102</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>8.009758</v>
-      </c>
-      <c r="G208" s="5" t="n">
-        <v>10.838333</v>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>13.433961</v>
-      </c>
-      <c r="I208" s="5" t="n">
-        <v>36.795182</v>
+        <v>-0.846332</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J208" s="5" t="n">
-        <v>58.361429</v>
+        <v>-10.109399</v>
       </c>
       <c r="K208" s="5" t="n">
-        <v>66.548333</v>
+        <v>-3.811682</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -23178,24 +23050,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$                         Total                                           equity                                                                                             1,752,179       12,160,000                          776,000              100,000     844,890         (10,109,399)       5,523,670     200,000        (3,811,682)       1,911,988                                                                               shareholders’</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>-5.2e-07</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -23212,15 +23084,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J209" s="5" t="n">
+        <v>-1.7e-07</v>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -23261,45 +23129,39 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$ Deficit (3,479,330) (10,109,399) (13,588,729)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>2.128562</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>8.009758</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>10.838333</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>13.433961</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>36.795182</v>
       </c>
       <c r="J210" s="5" t="n">
-        <v>-17.400411</v>
+        <v>58.361429</v>
       </c>
       <c r="K210" s="5" t="n">
-        <v>-3.811682</v>
+        <v>66.548333</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -23345,7 +23207,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>– total</t>
+          <t>$                         Total                                           equity                                                                                             1,752,179       12,160,000                          776,000              100,000     844,890         (10,109,399)       5,523,670     200,000        (3,811,682)       1,911,988                                                                               shareholders’</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -23423,12 +23285,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>$                        Share                                                                                                                                                                            (200,000)     200,000                                                                        receivable                                                                             (200,000)                                                                              subscriptions</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>$                        Share                                                                                                                                                                            (200,000)     200,000                                                                        receivable                                                                             (200,000)                                                                              subscriptions</t>
+          <t>$ Deficit (3,479,330) (10,109,399) (13,588,729)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -23457,15 +23319,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J212" s="5" t="n">
+        <v>-17.400411</v>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>-3.811682</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -23506,12 +23364,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>– –  –     –   – –                                                                                                                                                                                                                                                                                                                                                                                                                                              financial</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>$       692,867                                                                   (45,235)     844,890                       1,492,522                                       1,492,522                                          payment reserve                                                                                                                                                                                                      theseof                                                      Share-based                                                                                                                                                                                               part</t>
+          <t>– total</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -23589,12 +23447,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>– –  –     –   – –                                                                                                                                                                                                                                                                                                                                                                                                                                              financial</t>
+          <t>$                        Share                                                                                                                                                                            (200,000)     200,000                                                                        receivable                                                                             (200,000)                                                                              subscriptions</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>5        $                                                                                                                                                                                                                                                                                                                   integral                                                                                                                     976,000              145,235                                           Amount                   4,248,642       12,450,000                                                                                                                        17,819,877                                           17,819,877                                          capital                                                                                  anare</t>
+          <t>$                        Share                                                                                                                                                                            (200,000)     200,000                                                                        receivable                                                                             (200,000)                                                                              subscriptions</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -23677,7 +23535,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>of Share notes 800,000 400,000 Number shares 37,588,333 18,000,000 9,760,000</t>
+          <t>$       692,867                                                                   (45,235)     844,890                       1,492,522                                       1,492,522                                          payment reserve                                                                                                                                                                                                      theseof                                                      Share-based                                                                                                                                                                                               part</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -23706,11 +23564,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J215" s="5" t="n">
-        <v>66.548333</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>66.548333</v>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -23751,12 +23613,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>– –  –     –   – –                                                                                                                                                                                                                                                                                                                                                                                                                                              financial</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 11)</t>
+          <t>5        $                                                                                                                                                                                                                                                                                                                   integral                                                                                                                     976,000              145,235                                           Amount                   4,248,642       12,450,000                                                                                                                        17,819,877                                           17,819,877                                          capital                                                                                  anare</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -23780,8 +23642,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I216" s="5" t="n">
-        <v>0.045235</v>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -23832,19 +23696,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>– –  –     –   – –                                                                                                                                                                                                                                                                                                                                                                                                                                              financial</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>of Share notes 800,000 400,000 Number shares 37,588,333 18,000,000 9,760,000</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -23860,23 +23720,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" s="5" t="n">
-        <v>-0.010304</v>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J217" s="5" t="n">
+        <v>66.548333</v>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>66.548333</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -23917,12 +23775,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt</t>
+          <t>Share-based payments (Note 11)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -23947,7 +23805,7 @@
         </is>
       </c>
       <c r="I218" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.045235</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -24003,12 +23861,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income for the year</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -24027,10 +23885,12 @@
         </is>
       </c>
       <c r="H219" s="5" t="n">
-        <v>0.0009479999999999999</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>0.262852</v>
+        <v>-0.010304</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -24086,14 +23946,10 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Earnings per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Loss on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -24115,7 +23971,7 @@
         </is>
       </c>
       <c r="I220" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.0048</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -24166,17 +24022,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Note 13)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Net income and comprehensive income for the year</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -24189,18 +24045,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G221" s="5" t="n">
-        <v>0.010814</v>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>0.0009479999999999999</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>0.262852</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -24251,35 +24105,41 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Director and management compensation (Note 5)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
+          <t>Earnings per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F222" s="5" t="n">
-        <v>0.309833</v>
-      </c>
-      <c r="G222" s="5" t="n">
-        <v>0.020351</v>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I222" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -24330,17 +24190,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note 13)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>General and administrative (Note 5)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -24348,11 +24208,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F223" s="5" t="n">
-        <v>0.036866</v>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>0.035535</v>
+        <v>0.010814</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -24418,24 +24280,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Director and management compensation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>0.216984</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.309833</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>0.052922</v>
+        <v>0.020351</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -24496,17 +24352,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>General and administrative (Note 5)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -24515,10 +24371,10 @@
         </is>
       </c>
       <c r="F225" s="5" t="n">
-        <v>0.007639</v>
+        <v>0.036866</v>
       </c>
       <c r="G225" s="5" t="n">
-        <v>0.01874</v>
+        <v>0.035535</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -24579,27 +24435,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Note 5(f))</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="n">
+        <v>0.195095</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>-0.07065299999999999</v>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08074000000000001</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>0.052922</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -24665,71 +24521,642 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>0.007639</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Loss on settlement of debt (Note 5(f))</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>-0.07065299999999999</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
           <t>Earnings (loss) per share, basic and diluted</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="n">
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="n">
         <v>-1e-07</v>
       </c>
-      <c r="G227" s="5" t="n">
+      <c r="G229" s="5" t="n">
         <v>1e-08</v>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>General and administrative expenses (Note 5)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>0.092984</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>0.036866</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Unrealized foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>0.013738</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>0.007639</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
+        <v>-1.920291</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>-3.021311</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Deficit, end of year</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" s="5" t="n">
+        <v>-3.021311</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>-3.867643</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
